--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2022_valparaiso_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2022_valparaiso_provincial.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:15</t>
+    <t xml:space="preserve">2026-09-29 14:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2022_valparaiso_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2022_valparaiso_provincial.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:02</t>
+    <t xml:space="preserve">2026-09-29 18:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -508,7 +508,7 @@
         <v>90.66</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>55.18</v>
+        <v>55.19</v>
       </c>
     </row>
     <row r="3">
@@ -519,7 +519,7 @@
         <v>26.09</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>64.06</v>
+        <v>64.05</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>37.96</v>
@@ -561,10 +561,10 @@
         <v>11.63</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>53.58</v>
+        <v>53.57</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>41.95</v>
+        <v>41.94</v>
       </c>
     </row>
     <row r="7">
@@ -592,7 +592,7 @@
         <v>56.14</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>50.13</v>
+        <v>50.12</v>
       </c>
     </row>
     <row r="9">

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2022_valparaiso_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2022_valparaiso_provincial.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:42</t>
+    <t xml:space="preserve">2026-10-05 04:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -505,7 +505,7 @@
         <v>35.48</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>90.66</v>
+        <v>90.67</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>55.19</v>
@@ -519,10 +519,10 @@
         <v>26.09</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>64.05</v>
+        <v>64.06</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>37.96</v>
+        <v>37.97</v>
       </c>
     </row>
     <row r="4">
@@ -561,10 +561,10 @@
         <v>11.63</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>53.57</v>
+        <v>53.58</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>41.94</v>
+        <v>41.95</v>
       </c>
     </row>
     <row r="7">
@@ -589,10 +589,10 @@
         <v>6.02</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>56.14</v>
+        <v>56.15</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>50.12</v>
+        <v>50.13</v>
       </c>
     </row>
     <row r="9">
